--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/06,26/29,06,26 Останкино КИ и ЗПФ/расчеты Останкино ЗПФ/дв 29,06,26 лгрсч ост зпф.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/06,26/29,06,26 Останкино КИ и ЗПФ/расчеты Останкино ЗПФ/дв 29,06,26 лгрсч ост зпф.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\расчеты Останкино ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\06,26\29,06,26 Останкино КИ и ЗПФ\расчеты Останкино ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7650B87-C6B7-4CCB-B5C0-CB8A311993A9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD92F0B9-DA92-4935-9CCE-736FBE164E97}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="41">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -158,9 +158,6 @@
   </si>
   <si>
     <t>заказ</t>
-  </si>
-  <si>
-    <t>05,07,</t>
   </si>
 </sst>
 </file>
@@ -2961,7 +2958,7 @@
         <v>37</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
